--- a/.vscode/001.일정관리/WPC-1st-TOM-2025_주단위상세일정.xlsx
+++ b/.vscode/001.일정관리/WPC-1st-TOM-2025_주단위상세일정.xlsx
@@ -1,17 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24332"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\웹퍼블리셔과정_탐\github\WPC-626-TOM\001.일정관리\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDA5E2C3-50B7-4B5D-AC0C-F547B728AB44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="21795" windowHeight="14595"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hi-Media 반응형 웹퍼블리셔 1회차 주별 상세일정" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -27,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="118">
   <si>
     <t>3주차</t>
   </si>
@@ -390,11 +396,6 @@
   </si>
   <si>
     <t>HTML5 + CSS3 응용연습
-Javascript 응용 / 제이쿼리 기본</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>HTML5 + CSS3 응용연습
 제이쿼리 응용</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -511,26 +512,44 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>2차 PJ 테스트/수정/배포</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>2차 PJ 발표 / 산출물작업</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>2차 산출물작업</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>HTML5 + CSS3 응용연습</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>도깨비 PJ 프로토타이핑 / 코딩</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>2차 PJ UI 디자인</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>2차 PJ 프로토타입</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>HTML5 + CSS3 응용연습
+Javascript 응용</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>HTML5 + CSS3 응용연습
+제이쿼리 기본</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>1차 PJ 자체점검</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
     <numFmt numFmtId="176" formatCode="#\ &quot;일&quot;"/>
     <numFmt numFmtId="177" formatCode="&quot;총&quot;\ #\ &quot;일&quot;"/>
@@ -871,7 +890,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1038,12 +1057,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="1" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="1" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1073,9 +1086,9 @@
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
-    <cellStyle name="표준 2" xfId="2"/>
-    <cellStyle name="표준 3" xfId="3"/>
-    <cellStyle name="표준 4" xfId="1"/>
+    <cellStyle name="표준 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="표준 3" xfId="3" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
+    <cellStyle name="표준 4" xfId="1" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1133,7 +1146,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1166,9 +1179,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1201,6 +1231,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -1376,12 +1423,12 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:L43"/>
-  <sheetFormatPr defaultRowHeight="16.899999999999999"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="2.375" customWidth="1"/>
     <col min="2" max="2" width="7.25" style="2" bestFit="1" customWidth="1"/>
@@ -1397,43 +1444,43 @@
     <col min="12" max="12" width="10.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="17.25" thickBot="1"/>
-    <row r="2" spans="1:12" ht="53.25" customHeight="1" thickTop="1" thickBot="1">
-      <c r="B2" s="63" t="s">
+    <row r="1" spans="2:12" ht="17.25" thickBot="1"/>
+    <row r="2" spans="2:12" ht="53.25" customHeight="1" thickTop="1" thickBot="1">
+      <c r="B2" s="61" t="s">
         <v>48</v>
       </c>
-      <c r="C2" s="64"/>
-      <c r="D2" s="64"/>
-      <c r="E2" s="64"/>
-      <c r="F2" s="64"/>
-      <c r="G2" s="64"/>
-      <c r="H2" s="64"/>
-      <c r="I2" s="64"/>
-      <c r="J2" s="64"/>
-      <c r="K2" s="64"/>
-      <c r="L2" s="65"/>
-    </row>
-    <row r="3" spans="1:12" ht="18.75" customHeight="1" thickTop="1" thickBot="1">
-      <c r="B3" s="59"/>
-      <c r="C3" s="59"/>
-      <c r="D3" s="59"/>
-      <c r="E3" s="59"/>
-      <c r="F3" s="59"/>
-      <c r="G3" s="59"/>
-      <c r="H3" s="59"/>
-      <c r="I3" s="59"/>
-      <c r="J3" s="59"/>
-      <c r="K3" s="59"/>
-    </row>
-    <row r="4" spans="1:12" s="3" customFormat="1" ht="34.5" customHeight="1">
+      <c r="C2" s="62"/>
+      <c r="D2" s="62"/>
+      <c r="E2" s="62"/>
+      <c r="F2" s="62"/>
+      <c r="G2" s="62"/>
+      <c r="H2" s="62"/>
+      <c r="I2" s="62"/>
+      <c r="J2" s="62"/>
+      <c r="K2" s="62"/>
+      <c r="L2" s="63"/>
+    </row>
+    <row r="3" spans="2:12" ht="18.75" customHeight="1" thickTop="1" thickBot="1">
+      <c r="B3" s="57"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="57"/>
+      <c r="K3" s="57"/>
+    </row>
+    <row r="4" spans="2:12" s="3" customFormat="1" ht="34.5" customHeight="1">
       <c r="B4" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="60" t="s">
+      <c r="C4" s="58" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="60"/>
-      <c r="E4" s="60"/>
+      <c r="D4" s="58"/>
+      <c r="E4" s="58"/>
       <c r="F4" s="7" t="s">
         <v>11</v>
       </c>
@@ -1456,7 +1503,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:12" s="3" customFormat="1" ht="48" hidden="1" customHeight="1">
+    <row r="5" spans="2:12" s="3" customFormat="1" ht="48" hidden="1" customHeight="1">
       <c r="B5" s="9" t="s">
         <v>33</v>
       </c>
@@ -1484,7 +1531,7 @@
       </c>
       <c r="L5" s="15"/>
     </row>
-    <row r="6" spans="1:12" s="3" customFormat="1" ht="48" hidden="1" customHeight="1">
+    <row r="6" spans="2:12" s="3" customFormat="1" ht="48" hidden="1" customHeight="1">
       <c r="B6" s="9" t="s">
         <v>34</v>
       </c>
@@ -1512,7 +1559,7 @@
       </c>
       <c r="L6" s="15"/>
     </row>
-    <row r="7" spans="1:12" s="3" customFormat="1" ht="48" hidden="1" customHeight="1">
+    <row r="7" spans="2:12" s="3" customFormat="1" ht="48" hidden="1" customHeight="1">
       <c r="B7" s="9" t="s">
         <v>35</v>
       </c>
@@ -1540,7 +1587,7 @@
       </c>
       <c r="L7" s="15"/>
     </row>
-    <row r="8" spans="1:12" s="3" customFormat="1" ht="56.45" customHeight="1">
+    <row r="8" spans="2:12" s="3" customFormat="1" ht="56.45" customHeight="1">
       <c r="B8" s="40" t="s">
         <v>12</v>
       </c>
@@ -1570,7 +1617,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="9" spans="1:12" s="3" customFormat="1" ht="56.45" customHeight="1">
+    <row r="9" spans="2:12" s="3" customFormat="1" ht="56.45" customHeight="1">
       <c r="B9" s="47" t="s">
         <v>15</v>
       </c>
@@ -1595,14 +1642,14 @@
         <v>39</v>
       </c>
       <c r="J9" s="49" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K9" s="52" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L9" s="53"/>
     </row>
-    <row r="10" spans="1:12" s="3" customFormat="1" ht="56.45" customHeight="1">
+    <row r="10" spans="2:12" s="3" customFormat="1" ht="56.45" customHeight="1">
       <c r="B10" s="47" t="s">
         <v>0</v>
       </c>
@@ -1627,14 +1674,14 @@
         <v>38</v>
       </c>
       <c r="J10" s="49" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K10" s="52" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L10" s="53"/>
     </row>
-    <row r="11" spans="1:12" s="3" customFormat="1" ht="56.45" customHeight="1">
+    <row r="11" spans="2:12" s="3" customFormat="1" ht="56.45" customHeight="1">
       <c r="B11" s="47" t="s">
         <v>1</v>
       </c>
@@ -1659,14 +1706,14 @@
         <v>38</v>
       </c>
       <c r="J11" s="52" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K11" s="52" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="L11" s="53"/>
     </row>
-    <row r="12" spans="1:12" s="3" customFormat="1" ht="56.45" customHeight="1">
+    <row r="12" spans="2:12" s="3" customFormat="1" ht="56.45" customHeight="1">
       <c r="B12" s="47" t="s">
         <v>2</v>
       </c>
@@ -1688,17 +1735,17 @@
       </c>
       <c r="H12" s="51"/>
       <c r="I12" s="49" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="J12" s="52" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="K12" s="52" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L12" s="53"/>
     </row>
-    <row r="13" spans="1:12" s="3" customFormat="1" ht="56.45" customHeight="1">
+    <row r="13" spans="2:12" s="3" customFormat="1" ht="56.45" customHeight="1">
       <c r="B13" s="47" t="s">
         <v>3</v>
       </c>
@@ -1720,17 +1767,17 @@
       </c>
       <c r="H13" s="51"/>
       <c r="I13" s="49" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="J13" s="52" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K13" s="52" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="L13" s="53"/>
     </row>
-    <row r="14" spans="1:12" s="3" customFormat="1" ht="56.45" customHeight="1">
+    <row r="14" spans="2:12" s="3" customFormat="1" ht="56.45" customHeight="1">
       <c r="B14" s="47" t="s">
         <v>4</v>
       </c>
@@ -1750,21 +1797,21 @@
       <c r="G14" s="44" t="s">
         <v>55</v>
       </c>
-      <c r="H14" s="58" t="s">
+      <c r="H14" s="56" t="s">
         <v>54</v>
       </c>
       <c r="I14" s="52" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="J14" s="52" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K14" s="52" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="L14" s="46"/>
     </row>
-    <row r="15" spans="1:12" s="3" customFormat="1" ht="56.45" customHeight="1">
+    <row r="15" spans="2:12" s="3" customFormat="1" ht="56.45" customHeight="1">
       <c r="B15" s="47" t="s">
         <v>5</v>
       </c>
@@ -1786,86 +1833,86 @@
       </c>
       <c r="H15" s="51"/>
       <c r="I15" s="52" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="J15" s="49" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K15" s="52" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="L15" s="53"/>
     </row>
-    <row r="16" spans="1:12" s="3" customFormat="1" ht="56.45" customHeight="1">
-      <c r="A16" s="34"/>
-      <c r="B16" s="35" t="s">
+    <row r="16" spans="2:12" s="3" customFormat="1" ht="56.45" customHeight="1">
+      <c r="B16" s="47" t="s">
         <v>16</v>
       </c>
-      <c r="C16" s="36">
+      <c r="C16" s="48">
         <v>45887</v>
       </c>
-      <c r="D16" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="E16" s="36">
+      <c r="D16" s="49" t="s">
+        <v>6</v>
+      </c>
+      <c r="E16" s="48">
         <v>45891</v>
       </c>
-      <c r="F16" s="38">
+      <c r="F16" s="50">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="G16" s="33" t="s">
+      <c r="G16" s="44" t="s">
         <v>57</v>
       </c>
-      <c r="H16" s="56"/>
-      <c r="I16" s="39" t="s">
-        <v>104</v>
-      </c>
-      <c r="J16" s="37" t="s">
-        <v>106</v>
-      </c>
-      <c r="K16" s="39" t="s">
-        <v>95</v>
-      </c>
-      <c r="L16" s="57"/>
-    </row>
-    <row r="17" spans="2:12" s="3" customFormat="1" ht="56.45" customHeight="1">
-      <c r="B17" s="17" t="s">
+      <c r="H16" s="51"/>
+      <c r="I16" s="52" t="s">
+        <v>103</v>
+      </c>
+      <c r="J16" s="49" t="s">
+        <v>105</v>
+      </c>
+      <c r="K16" s="52" t="s">
+        <v>94</v>
+      </c>
+      <c r="L16" s="53"/>
+    </row>
+    <row r="17" spans="1:12" s="3" customFormat="1" ht="56.45" customHeight="1">
+      <c r="A17" s="34"/>
+      <c r="B17" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="C17" s="18">
+      <c r="C17" s="36">
         <v>45894</v>
       </c>
-      <c r="D17" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="E17" s="18">
+      <c r="D17" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="E17" s="36">
         <v>45898</v>
       </c>
-      <c r="F17" s="20">
+      <c r="F17" s="38">
         <f>DAYS360(C17,E17)+1</f>
         <v>5</v>
       </c>
-      <c r="G17" s="16" t="s">
+      <c r="G17" s="33" t="s">
         <v>58</v>
       </c>
       <c r="H17" s="30" t="s">
         <v>61</v>
       </c>
-      <c r="I17" s="22" t="s">
-        <v>40</v>
-      </c>
-      <c r="J17" s="54" t="s">
-        <v>107</v>
-      </c>
-      <c r="K17" s="22" t="s">
+      <c r="I17" s="39" t="s">
+        <v>103</v>
+      </c>
+      <c r="J17" s="39" t="s">
+        <v>106</v>
+      </c>
+      <c r="K17" s="39" t="s">
         <v>85</v>
       </c>
       <c r="L17" s="28" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="18" spans="2:12" s="3" customFormat="1" ht="56.45" customHeight="1">
+    <row r="18" spans="1:12" s="3" customFormat="1" ht="56.45" customHeight="1">
       <c r="B18" s="17" t="s">
         <v>18</v>
       </c>
@@ -1887,17 +1934,17 @@
       </c>
       <c r="H18" s="21"/>
       <c r="I18" s="22" t="s">
-        <v>40</v>
+        <v>112</v>
       </c>
       <c r="J18" s="22" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="K18" s="22" t="s">
         <v>85</v>
       </c>
       <c r="L18" s="23"/>
     </row>
-    <row r="19" spans="2:12" s="3" customFormat="1" ht="56.45" customHeight="1">
+    <row r="19" spans="1:12" s="3" customFormat="1" ht="56.45" customHeight="1">
       <c r="B19" s="17" t="s">
         <v>19</v>
       </c>
@@ -1924,14 +1971,14 @@
         <v>42</v>
       </c>
       <c r="J19" s="22" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K19" s="22" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="L19" s="23"/>
     </row>
-    <row r="20" spans="2:12" s="3" customFormat="1" ht="56.45" customHeight="1">
+    <row r="20" spans="1:12" s="3" customFormat="1" ht="56.45" customHeight="1">
       <c r="B20" s="17" t="s">
         <v>20</v>
       </c>
@@ -1958,14 +2005,14 @@
         <v>40</v>
       </c>
       <c r="J20" s="22" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K20" s="22" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="L20" s="23"/>
     </row>
-    <row r="21" spans="2:12" s="3" customFormat="1" ht="56.45" customHeight="1">
+    <row r="21" spans="1:12" s="3" customFormat="1" ht="56.45" customHeight="1">
       <c r="B21" s="17" t="s">
         <v>21</v>
       </c>
@@ -1990,14 +2037,14 @@
         <v>43</v>
       </c>
       <c r="J21" s="54" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="K21" s="22" t="s">
-        <v>87</v>
+        <v>115</v>
       </c>
       <c r="L21" s="23"/>
     </row>
-    <row r="22" spans="2:12" s="3" customFormat="1" ht="56.45" customHeight="1">
+    <row r="22" spans="1:12" s="3" customFormat="1" ht="56.45" customHeight="1">
       <c r="B22" s="17" t="s">
         <v>22</v>
       </c>
@@ -2022,14 +2069,14 @@
         <v>41</v>
       </c>
       <c r="J22" s="22" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="K22" s="22" t="s">
-        <v>87</v>
+        <v>116</v>
       </c>
       <c r="L22" s="23"/>
     </row>
-    <row r="23" spans="2:12" s="3" customFormat="1" ht="56.45" customHeight="1">
+    <row r="23" spans="1:12" s="3" customFormat="1" ht="56.45" customHeight="1">
       <c r="B23" s="17" t="s">
         <v>23</v>
       </c>
@@ -2054,14 +2101,14 @@
         <v>41</v>
       </c>
       <c r="J23" s="22" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="K23" s="22" t="s">
-        <v>87</v>
+        <v>116</v>
       </c>
       <c r="L23" s="23"/>
     </row>
-    <row r="24" spans="2:12" s="3" customFormat="1" ht="56.45" customHeight="1">
+    <row r="24" spans="1:12" s="3" customFormat="1" ht="56.45" customHeight="1">
       <c r="B24" s="17" t="s">
         <v>24</v>
       </c>
@@ -2088,14 +2135,14 @@
         <v>44</v>
       </c>
       <c r="J24" s="22" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="K24" s="22" t="s">
-        <v>87</v>
+        <v>116</v>
       </c>
       <c r="L24" s="23"/>
     </row>
-    <row r="25" spans="2:12" s="3" customFormat="1" ht="56.45" customHeight="1">
+    <row r="25" spans="1:12" s="3" customFormat="1" ht="56.45" customHeight="1">
       <c r="B25" s="17" t="s">
         <v>25</v>
       </c>
@@ -2122,14 +2169,14 @@
         <v>45</v>
       </c>
       <c r="J25" s="22" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="K25" s="22" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L25" s="23"/>
     </row>
-    <row r="26" spans="2:12" s="3" customFormat="1" ht="56.45" customHeight="1">
+    <row r="26" spans="1:12" s="3" customFormat="1" ht="56.45" customHeight="1">
       <c r="B26" s="17" t="s">
         <v>26</v>
       </c>
@@ -2156,16 +2203,16 @@
         <v>45</v>
       </c>
       <c r="J26" s="22" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="K26" s="22" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L26" s="29" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="27" spans="2:12" ht="56.45" customHeight="1">
+    <row r="27" spans="1:12" ht="56.45" customHeight="1">
       <c r="B27" s="17" t="s">
         <v>27</v>
       </c>
@@ -2192,14 +2239,14 @@
         <v>46</v>
       </c>
       <c r="J27" s="19" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="K27" s="22" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L27" s="25"/>
     </row>
-    <row r="28" spans="2:12" ht="56.45" customHeight="1">
+    <row r="28" spans="1:12" ht="56.45" customHeight="1">
       <c r="B28" s="17" t="s">
         <v>28</v>
       </c>
@@ -2224,14 +2271,14 @@
         <v>47</v>
       </c>
       <c r="J28" s="19" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="K28" s="22" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L28" s="24"/>
     </row>
-    <row r="29" spans="2:12" ht="56.45" customHeight="1">
+    <row r="29" spans="1:12" ht="56.45" customHeight="1">
       <c r="B29" s="17" t="s">
         <v>29</v>
       </c>
@@ -2258,16 +2305,16 @@
         <v>47</v>
       </c>
       <c r="J29" s="19" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="K29" s="22" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L29" s="27" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="30" spans="2:12" ht="47.25" customHeight="1" thickBot="1">
+    <row r="30" spans="1:12" ht="47.25" customHeight="1" thickBot="1">
       <c r="C30" s="1"/>
       <c r="E30" s="1"/>
       <c r="F30" s="4">
@@ -2275,33 +2322,33 @@
         <v>95</v>
       </c>
     </row>
-    <row r="31" spans="2:12" ht="21.75" customHeight="1">
-      <c r="B31" s="61" t="s">
+    <row r="31" spans="1:12" ht="21.75" customHeight="1">
+      <c r="B31" s="59" t="s">
         <v>13</v>
       </c>
-      <c r="C31" s="61"/>
-      <c r="D31" s="61"/>
-      <c r="E31" s="61"/>
-      <c r="F31" s="61"/>
-      <c r="G31" s="61"/>
-      <c r="H31" s="61"/>
-      <c r="I31" s="61"/>
-      <c r="J31" s="61"/>
-      <c r="K31" s="61"/>
-    </row>
-    <row r="32" spans="2:12" s="5" customFormat="1" ht="27">
-      <c r="B32" s="62" t="s">
+      <c r="C31" s="59"/>
+      <c r="D31" s="59"/>
+      <c r="E31" s="59"/>
+      <c r="F31" s="59"/>
+      <c r="G31" s="59"/>
+      <c r="H31" s="59"/>
+      <c r="I31" s="59"/>
+      <c r="J31" s="59"/>
+      <c r="K31" s="59"/>
+    </row>
+    <row r="32" spans="1:12" s="5" customFormat="1" ht="26.25">
+      <c r="B32" s="60" t="s">
         <v>83</v>
       </c>
-      <c r="C32" s="62"/>
-      <c r="D32" s="62"/>
-      <c r="E32" s="62"/>
-      <c r="F32" s="62"/>
-      <c r="G32" s="62"/>
-      <c r="H32" s="62"/>
-      <c r="I32" s="62"/>
-      <c r="J32" s="62"/>
-      <c r="K32" s="62"/>
+      <c r="C32" s="60"/>
+      <c r="D32" s="60"/>
+      <c r="E32" s="60"/>
+      <c r="F32" s="60"/>
+      <c r="G32" s="60"/>
+      <c r="H32" s="60"/>
+      <c r="I32" s="60"/>
+      <c r="J32" s="60"/>
+      <c r="K32" s="60"/>
     </row>
     <row r="43" spans="9:9">
       <c r="I43" s="2" t="s">
@@ -2323,9 +2370,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="16.899999999999999"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <sheetData/>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2333,9 +2380,9 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="16.899999999999999"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <sheetData/>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/.vscode/001.일정관리/WPC-1st-TOM-2025_주단위상세일정.xlsx
+++ b/.vscode/001.일정관리/WPC-1st-TOM-2025_주단위상세일정.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\웹퍼블리셔과정_탐\github\WPC-626-TOM\001.일정관리\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDA5E2C3-50B7-4B5D-AC0C-F547B728AB44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AEBD93F-C64A-4613-9B73-D2980526A466}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hi-Media 반응형 웹퍼블리셔 1회차 주별 상세일정" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="113">
   <si>
     <t>3주차</t>
   </si>
@@ -176,23 +176,6 @@
   </si>
   <si>
     <t>도깨비 PJ 상세코딩</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>보그 PJ 상세코딩</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>도깨비 PJ 상세코딩</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>도깨비 PJ 상세코딩
-보그 PJ 분석/설계</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>보그 PJ 상세코딩</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
@@ -504,10 +487,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>2차 주제선정 및 분석/설계</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>2차 PJ 상세코딩</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -517,23 +496,6 @@
   </si>
   <si>
     <t>HTML5 + CSS3 응용연습</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>도깨비 PJ 프로토타이핑 / 코딩</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>2차 PJ UI 디자인</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>2차 PJ 프로토타입</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>HTML5 + CSS3 응용연습
-Javascript 응용</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
@@ -542,7 +504,26 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>1차 PJ 자체점검</t>
+    <t>도깨비 PJ 목업 + 상세코딩</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>보그 PJ 분석/설계 + 상세코딩</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>1차 상세코딩
+2차 주제선정</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>1차 상세코딩
+2차 PJ 디자인 &amp; 프로토타입</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>HTML5 + CSS3 응용연습
+Javascript 응용 / 제이쿼리 기본</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -659,7 +640,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -686,24 +667,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -722,7 +685,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
+        <fgColor rgb="FFCCFF33"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCCFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCECFF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -972,94 +947,94 @@
     <xf numFmtId="178" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="10" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="10" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="176" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="10" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="10" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="7" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="176" fontId="0" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1092,6 +1067,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFCCECFF"/>
+      <color rgb="FFFFCCFF"/>
+      <color rgb="FFCCFF33"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1447,7 +1429,7 @@
     <row r="1" spans="2:12" ht="17.25" thickBot="1"/>
     <row r="2" spans="2:12" ht="53.25" customHeight="1" thickTop="1" thickBot="1">
       <c r="B2" s="61" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C2" s="62"/>
       <c r="D2" s="62"/>
@@ -1488,7 +1470,7 @@
         <v>10</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="I4" s="7" t="s">
         <v>31</v>
@@ -1588,493 +1570,493 @@
       <c r="L7" s="15"/>
     </row>
     <row r="8" spans="2:12" s="3" customFormat="1" ht="56.45" customHeight="1">
-      <c r="B8" s="40" t="s">
+      <c r="B8" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="41">
+      <c r="C8" s="35">
         <v>45834</v>
       </c>
-      <c r="D8" s="42" t="s">
-        <v>6</v>
-      </c>
-      <c r="E8" s="41">
+      <c r="D8" s="36" t="s">
+        <v>6</v>
+      </c>
+      <c r="E8" s="35">
         <v>45835</v>
       </c>
-      <c r="F8" s="43">
+      <c r="F8" s="37">
         <f>DAYS360(C8,E8)+1</f>
         <v>2</v>
       </c>
-      <c r="G8" s="44" t="s">
-        <v>49</v>
-      </c>
-      <c r="H8" s="42"/>
-      <c r="I8" s="42"/>
-      <c r="J8" s="42"/>
-      <c r="K8" s="45" t="s">
-        <v>84</v>
-      </c>
-      <c r="L8" s="46" t="s">
-        <v>74</v>
+      <c r="G8" s="38" t="s">
+        <v>45</v>
+      </c>
+      <c r="H8" s="36"/>
+      <c r="I8" s="36"/>
+      <c r="J8" s="36"/>
+      <c r="K8" s="39" t="s">
+        <v>80</v>
+      </c>
+      <c r="L8" s="40" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="9" spans="2:12" s="3" customFormat="1" ht="56.45" customHeight="1">
-      <c r="B9" s="47" t="s">
+      <c r="B9" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="48">
+      <c r="C9" s="42">
         <v>45838</v>
       </c>
-      <c r="D9" s="49" t="s">
-        <v>6</v>
-      </c>
-      <c r="E9" s="48">
+      <c r="D9" s="43" t="s">
+        <v>6</v>
+      </c>
+      <c r="E9" s="42">
         <v>45842</v>
       </c>
-      <c r="F9" s="50">
+      <c r="F9" s="44">
         <f t="shared" ref="F9:F27" si="0">DAYS360(C9,E9)+1</f>
         <v>5</v>
       </c>
-      <c r="G9" s="44" t="s">
-        <v>50</v>
-      </c>
-      <c r="H9" s="51"/>
-      <c r="I9" s="49" t="s">
+      <c r="G9" s="38" t="s">
+        <v>46</v>
+      </c>
+      <c r="H9" s="45"/>
+      <c r="I9" s="43" t="s">
         <v>39</v>
       </c>
-      <c r="J9" s="49" t="s">
-        <v>88</v>
-      </c>
-      <c r="K9" s="52" t="s">
-        <v>95</v>
-      </c>
-      <c r="L9" s="53"/>
+      <c r="J9" s="43" t="s">
+        <v>84</v>
+      </c>
+      <c r="K9" s="46" t="s">
+        <v>91</v>
+      </c>
+      <c r="L9" s="47"/>
     </row>
     <row r="10" spans="2:12" s="3" customFormat="1" ht="56.45" customHeight="1">
-      <c r="B10" s="47" t="s">
+      <c r="B10" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="C10" s="48">
+      <c r="C10" s="42">
         <v>45845</v>
       </c>
-      <c r="D10" s="49" t="s">
-        <v>6</v>
-      </c>
-      <c r="E10" s="48">
+      <c r="D10" s="43" t="s">
+        <v>6</v>
+      </c>
+      <c r="E10" s="42">
         <v>45849</v>
       </c>
-      <c r="F10" s="50">
+      <c r="F10" s="44">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="G10" s="44" t="s">
-        <v>51</v>
-      </c>
-      <c r="H10" s="51"/>
-      <c r="I10" s="49" t="s">
+      <c r="G10" s="38" t="s">
+        <v>47</v>
+      </c>
+      <c r="H10" s="45"/>
+      <c r="I10" s="43" t="s">
         <v>38</v>
       </c>
-      <c r="J10" s="49" t="s">
-        <v>87</v>
-      </c>
-      <c r="K10" s="52" t="s">
-        <v>96</v>
-      </c>
-      <c r="L10" s="53"/>
+      <c r="J10" s="43" t="s">
+        <v>83</v>
+      </c>
+      <c r="K10" s="46" t="s">
+        <v>92</v>
+      </c>
+      <c r="L10" s="47"/>
     </row>
     <row r="11" spans="2:12" s="3" customFormat="1" ht="56.45" customHeight="1">
-      <c r="B11" s="47" t="s">
+      <c r="B11" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="C11" s="48">
+      <c r="C11" s="42">
         <v>45852</v>
       </c>
-      <c r="D11" s="49" t="s">
-        <v>6</v>
-      </c>
-      <c r="E11" s="48">
+      <c r="D11" s="43" t="s">
+        <v>6</v>
+      </c>
+      <c r="E11" s="42">
         <v>45856</v>
       </c>
-      <c r="F11" s="50">
+      <c r="F11" s="44">
         <f>DAYS360(C11,E11)+1</f>
         <v>5</v>
       </c>
-      <c r="G11" s="44" t="s">
-        <v>52</v>
-      </c>
-      <c r="H11" s="55"/>
-      <c r="I11" s="49" t="s">
+      <c r="G11" s="38" t="s">
+        <v>48</v>
+      </c>
+      <c r="H11" s="48"/>
+      <c r="I11" s="43" t="s">
         <v>38</v>
       </c>
-      <c r="J11" s="52" t="s">
-        <v>97</v>
-      </c>
-      <c r="K11" s="52" t="s">
-        <v>91</v>
-      </c>
-      <c r="L11" s="53"/>
+      <c r="J11" s="46" t="s">
+        <v>93</v>
+      </c>
+      <c r="K11" s="46" t="s">
+        <v>87</v>
+      </c>
+      <c r="L11" s="47"/>
     </row>
     <row r="12" spans="2:12" s="3" customFormat="1" ht="56.45" customHeight="1">
-      <c r="B12" s="47" t="s">
+      <c r="B12" s="41" t="s">
         <v>2</v>
       </c>
-      <c r="C12" s="48">
+      <c r="C12" s="42">
         <v>45859</v>
       </c>
-      <c r="D12" s="49" t="s">
-        <v>6</v>
-      </c>
-      <c r="E12" s="48">
+      <c r="D12" s="43" t="s">
+        <v>6</v>
+      </c>
+      <c r="E12" s="42">
         <v>45863</v>
       </c>
-      <c r="F12" s="50">
+      <c r="F12" s="44">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="G12" s="44" t="s">
-        <v>53</v>
-      </c>
-      <c r="H12" s="51"/>
-      <c r="I12" s="49" t="s">
-        <v>100</v>
-      </c>
-      <c r="J12" s="52" t="s">
-        <v>99</v>
-      </c>
-      <c r="K12" s="52" t="s">
-        <v>92</v>
-      </c>
-      <c r="L12" s="53"/>
+      <c r="G12" s="38" t="s">
+        <v>49</v>
+      </c>
+      <c r="H12" s="45"/>
+      <c r="I12" s="43" t="s">
+        <v>96</v>
+      </c>
+      <c r="J12" s="46" t="s">
+        <v>95</v>
+      </c>
+      <c r="K12" s="46" t="s">
+        <v>88</v>
+      </c>
+      <c r="L12" s="47"/>
     </row>
     <row r="13" spans="2:12" s="3" customFormat="1" ht="56.45" customHeight="1">
-      <c r="B13" s="47" t="s">
+      <c r="B13" s="41" t="s">
         <v>3</v>
       </c>
-      <c r="C13" s="48">
+      <c r="C13" s="42">
         <v>45866</v>
       </c>
-      <c r="D13" s="49" t="s">
-        <v>6</v>
-      </c>
-      <c r="E13" s="48">
+      <c r="D13" s="43" t="s">
+        <v>6</v>
+      </c>
+      <c r="E13" s="42">
         <v>45867</v>
       </c>
-      <c r="F13" s="50">
+      <c r="F13" s="44">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="G13" s="44" t="s">
-        <v>53</v>
-      </c>
-      <c r="H13" s="51"/>
-      <c r="I13" s="49" t="s">
-        <v>100</v>
-      </c>
-      <c r="J13" s="52" t="s">
-        <v>89</v>
-      </c>
-      <c r="K13" s="52" t="s">
-        <v>98</v>
-      </c>
-      <c r="L13" s="53"/>
+      <c r="G13" s="38" t="s">
+        <v>49</v>
+      </c>
+      <c r="H13" s="45"/>
+      <c r="I13" s="43" t="s">
+        <v>96</v>
+      </c>
+      <c r="J13" s="46" t="s">
+        <v>85</v>
+      </c>
+      <c r="K13" s="46" t="s">
+        <v>94</v>
+      </c>
+      <c r="L13" s="47"/>
     </row>
     <row r="14" spans="2:12" s="3" customFormat="1" ht="56.45" customHeight="1">
-      <c r="B14" s="47" t="s">
+      <c r="B14" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="C14" s="48">
+      <c r="C14" s="42">
         <v>45873</v>
       </c>
-      <c r="D14" s="49" t="s">
-        <v>6</v>
-      </c>
-      <c r="E14" s="48">
+      <c r="D14" s="43" t="s">
+        <v>6</v>
+      </c>
+      <c r="E14" s="42">
         <v>45877</v>
       </c>
-      <c r="F14" s="50">
+      <c r="F14" s="44">
         <f>DAYS360(C14,E14)+1</f>
         <v>5</v>
       </c>
-      <c r="G14" s="44" t="s">
-        <v>55</v>
-      </c>
-      <c r="H14" s="56" t="s">
-        <v>54</v>
-      </c>
-      <c r="I14" s="52" t="s">
-        <v>101</v>
-      </c>
-      <c r="J14" s="52" t="s">
-        <v>90</v>
-      </c>
-      <c r="K14" s="52" t="s">
-        <v>93</v>
-      </c>
-      <c r="L14" s="46"/>
+      <c r="G14" s="38" t="s">
+        <v>51</v>
+      </c>
+      <c r="H14" s="49" t="s">
+        <v>50</v>
+      </c>
+      <c r="I14" s="46" t="s">
+        <v>97</v>
+      </c>
+      <c r="J14" s="46" t="s">
+        <v>86</v>
+      </c>
+      <c r="K14" s="46" t="s">
+        <v>89</v>
+      </c>
+      <c r="L14" s="40"/>
     </row>
     <row r="15" spans="2:12" s="3" customFormat="1" ht="56.45" customHeight="1">
-      <c r="B15" s="47" t="s">
+      <c r="B15" s="41" t="s">
         <v>5</v>
       </c>
-      <c r="C15" s="48">
+      <c r="C15" s="42">
         <v>45880</v>
       </c>
-      <c r="D15" s="49" t="s">
-        <v>6</v>
-      </c>
-      <c r="E15" s="48">
+      <c r="D15" s="43" t="s">
+        <v>6</v>
+      </c>
+      <c r="E15" s="42">
         <v>45883</v>
       </c>
-      <c r="F15" s="50">
+      <c r="F15" s="44">
         <f>DAYS360(C15,E15)+1</f>
         <v>4</v>
       </c>
-      <c r="G15" s="44" t="s">
-        <v>56</v>
-      </c>
-      <c r="H15" s="51"/>
-      <c r="I15" s="52" t="s">
-        <v>102</v>
-      </c>
-      <c r="J15" s="49" t="s">
-        <v>104</v>
-      </c>
-      <c r="K15" s="52" t="s">
-        <v>111</v>
-      </c>
-      <c r="L15" s="53"/>
+      <c r="G15" s="38" t="s">
+        <v>52</v>
+      </c>
+      <c r="H15" s="45"/>
+      <c r="I15" s="46" t="s">
+        <v>98</v>
+      </c>
+      <c r="J15" s="43" t="s">
+        <v>100</v>
+      </c>
+      <c r="K15" s="46" t="s">
+        <v>106</v>
+      </c>
+      <c r="L15" s="47"/>
     </row>
     <row r="16" spans="2:12" s="3" customFormat="1" ht="56.45" customHeight="1">
-      <c r="B16" s="47" t="s">
+      <c r="B16" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="C16" s="48">
+      <c r="C16" s="42">
         <v>45887</v>
       </c>
-      <c r="D16" s="49" t="s">
-        <v>6</v>
-      </c>
-      <c r="E16" s="48">
+      <c r="D16" s="43" t="s">
+        <v>6</v>
+      </c>
+      <c r="E16" s="42">
         <v>45891</v>
       </c>
-      <c r="F16" s="50">
+      <c r="F16" s="44">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="G16" s="44" t="s">
-        <v>57</v>
-      </c>
-      <c r="H16" s="51"/>
-      <c r="I16" s="52" t="s">
-        <v>103</v>
-      </c>
-      <c r="J16" s="49" t="s">
-        <v>105</v>
-      </c>
-      <c r="K16" s="52" t="s">
-        <v>94</v>
-      </c>
-      <c r="L16" s="53"/>
+      <c r="G16" s="38" t="s">
+        <v>53</v>
+      </c>
+      <c r="H16" s="45"/>
+      <c r="I16" s="46" t="s">
+        <v>99</v>
+      </c>
+      <c r="J16" s="43" t="s">
+        <v>101</v>
+      </c>
+      <c r="K16" s="46" t="s">
+        <v>90</v>
+      </c>
+      <c r="L16" s="47"/>
     </row>
     <row r="17" spans="1:12" s="3" customFormat="1" ht="56.45" customHeight="1">
-      <c r="A17" s="34"/>
-      <c r="B17" s="35" t="s">
+      <c r="B17" s="41" t="s">
         <v>17</v>
       </c>
-      <c r="C17" s="36">
+      <c r="C17" s="42">
         <v>45894</v>
       </c>
-      <c r="D17" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="E17" s="36">
+      <c r="D17" s="43" t="s">
+        <v>6</v>
+      </c>
+      <c r="E17" s="42">
         <v>45898</v>
       </c>
-      <c r="F17" s="38">
+      <c r="F17" s="44">
         <f>DAYS360(C17,E17)+1</f>
         <v>5</v>
       </c>
-      <c r="G17" s="33" t="s">
-        <v>58</v>
-      </c>
-      <c r="H17" s="30" t="s">
-        <v>61</v>
-      </c>
-      <c r="I17" s="39" t="s">
-        <v>103</v>
-      </c>
-      <c r="J17" s="39" t="s">
-        <v>106</v>
-      </c>
-      <c r="K17" s="39" t="s">
-        <v>85</v>
-      </c>
-      <c r="L17" s="28" t="s">
-        <v>75</v>
+      <c r="G17" s="38" t="s">
+        <v>54</v>
+      </c>
+      <c r="H17" s="49" t="s">
+        <v>57</v>
+      </c>
+      <c r="I17" s="46" t="s">
+        <v>99</v>
+      </c>
+      <c r="J17" s="46" t="s">
+        <v>102</v>
+      </c>
+      <c r="K17" s="46" t="s">
+        <v>81</v>
+      </c>
+      <c r="L17" s="40" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="18" spans="1:12" s="3" customFormat="1" ht="56.45" customHeight="1">
-      <c r="B18" s="17" t="s">
+      <c r="B18" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="C18" s="18">
+      <c r="C18" s="42">
         <v>45901</v>
       </c>
-      <c r="D18" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="E18" s="18">
+      <c r="D18" s="43" t="s">
+        <v>6</v>
+      </c>
+      <c r="E18" s="42">
         <v>45905</v>
       </c>
-      <c r="F18" s="20">
+      <c r="F18" s="44">
         <f>DAYS360(C18,E18)+1</f>
         <v>5</v>
       </c>
-      <c r="G18" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="H18" s="21"/>
-      <c r="I18" s="22" t="s">
-        <v>112</v>
-      </c>
-      <c r="J18" s="22" t="s">
-        <v>106</v>
-      </c>
-      <c r="K18" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="L18" s="23"/>
+      <c r="G18" s="38" t="s">
+        <v>55</v>
+      </c>
+      <c r="H18" s="45"/>
+      <c r="I18" s="46" t="s">
+        <v>99</v>
+      </c>
+      <c r="J18" s="46" t="s">
+        <v>102</v>
+      </c>
+      <c r="K18" s="46" t="s">
+        <v>81</v>
+      </c>
+      <c r="L18" s="47"/>
     </row>
     <row r="19" spans="1:12" s="3" customFormat="1" ht="56.45" customHeight="1">
-      <c r="B19" s="17" t="s">
+      <c r="B19" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="C19" s="18">
+      <c r="C19" s="42">
         <v>45908</v>
       </c>
-      <c r="D19" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="E19" s="18">
+      <c r="D19" s="43" t="s">
+        <v>6</v>
+      </c>
+      <c r="E19" s="42">
         <v>45912</v>
       </c>
-      <c r="F19" s="20">
+      <c r="F19" s="44">
         <f>DAYS360(C19,E19)+1</f>
         <v>5</v>
       </c>
-      <c r="G19" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="H19" s="30" t="s">
-        <v>62</v>
-      </c>
-      <c r="I19" s="22" t="s">
-        <v>42</v>
-      </c>
-      <c r="J19" s="22" t="s">
-        <v>107</v>
-      </c>
-      <c r="K19" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="L19" s="23"/>
+      <c r="G19" s="38" t="s">
+        <v>59</v>
+      </c>
+      <c r="H19" s="49" t="s">
+        <v>58</v>
+      </c>
+      <c r="I19" s="46" t="s">
+        <v>108</v>
+      </c>
+      <c r="J19" s="46" t="s">
+        <v>103</v>
+      </c>
+      <c r="K19" s="46" t="s">
+        <v>81</v>
+      </c>
+      <c r="L19" s="47"/>
     </row>
     <row r="20" spans="1:12" s="3" customFormat="1" ht="56.45" customHeight="1">
-      <c r="B20" s="17" t="s">
+      <c r="B20" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C20" s="18">
+      <c r="C20" s="42">
         <v>45915</v>
       </c>
-      <c r="D20" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="E20" s="18">
+      <c r="D20" s="43" t="s">
+        <v>6</v>
+      </c>
+      <c r="E20" s="42">
         <v>45919</v>
       </c>
-      <c r="F20" s="20">
+      <c r="F20" s="44">
         <f>DAYS360(C20,E20)+1</f>
         <v>5</v>
       </c>
-      <c r="G20" s="16" t="s">
-        <v>64</v>
-      </c>
-      <c r="H20" s="30" t="s">
-        <v>77</v>
-      </c>
-      <c r="I20" s="22" t="s">
+      <c r="G20" s="38" t="s">
+        <v>60</v>
+      </c>
+      <c r="H20" s="56" t="s">
+        <v>73</v>
+      </c>
+      <c r="I20" s="46" t="s">
         <v>40</v>
       </c>
-      <c r="J20" s="22" t="s">
-        <v>107</v>
-      </c>
-      <c r="K20" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="L20" s="23"/>
+      <c r="J20" s="46" t="s">
+        <v>103</v>
+      </c>
+      <c r="K20" s="46" t="s">
+        <v>81</v>
+      </c>
+      <c r="L20" s="47"/>
     </row>
     <row r="21" spans="1:12" s="3" customFormat="1" ht="56.45" customHeight="1">
-      <c r="B21" s="17" t="s">
+      <c r="B21" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="C21" s="18">
+      <c r="C21" s="42">
         <v>45922</v>
       </c>
-      <c r="D21" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="E21" s="18">
+      <c r="D21" s="43" t="s">
+        <v>6</v>
+      </c>
+      <c r="E21" s="42">
         <v>45926</v>
       </c>
-      <c r="F21" s="20">
+      <c r="F21" s="44">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="G21" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="H21" s="21"/>
-      <c r="I21" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="J21" s="54" t="s">
-        <v>117</v>
-      </c>
-      <c r="K21" s="22" t="s">
-        <v>115</v>
-      </c>
-      <c r="L21" s="23"/>
+      <c r="G21" s="38" t="s">
+        <v>61</v>
+      </c>
+      <c r="H21" s="45"/>
+      <c r="I21" s="46" t="s">
+        <v>40</v>
+      </c>
+      <c r="J21" s="46" t="s">
+        <v>103</v>
+      </c>
+      <c r="K21" s="46" t="s">
+        <v>112</v>
+      </c>
+      <c r="L21" s="47"/>
     </row>
     <row r="22" spans="1:12" s="3" customFormat="1" ht="56.45" customHeight="1">
-      <c r="B22" s="17" t="s">
+      <c r="A22" s="28"/>
+      <c r="B22" s="29" t="s">
         <v>22</v>
       </c>
-      <c r="C22" s="18">
+      <c r="C22" s="30">
         <v>45929</v>
       </c>
-      <c r="D22" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="E22" s="18">
+      <c r="D22" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="E22" s="30">
         <v>45932</v>
       </c>
       <c r="F22" s="32">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="G22" s="16" t="s">
-        <v>66</v>
-      </c>
-      <c r="H22" s="21"/>
-      <c r="I22" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="J22" s="22" t="s">
-        <v>108</v>
-      </c>
-      <c r="K22" s="22" t="s">
-        <v>116</v>
-      </c>
-      <c r="L22" s="23"/>
+      <c r="G22" s="27" t="s">
+        <v>62</v>
+      </c>
+      <c r="H22" s="55"/>
+      <c r="I22" s="33" t="s">
+        <v>40</v>
+      </c>
+      <c r="J22" s="33" t="s">
+        <v>103</v>
+      </c>
+      <c r="K22" s="33" t="s">
+        <v>107</v>
+      </c>
+      <c r="L22" s="50"/>
     </row>
     <row r="23" spans="1:12" s="3" customFormat="1" ht="56.45" customHeight="1">
       <c r="B23" s="17" t="s">
@@ -2089,22 +2071,22 @@
       <c r="E23" s="18">
         <v>45940</v>
       </c>
-      <c r="F23" s="32">
+      <c r="F23" s="54">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="G23" s="16" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="H23" s="21"/>
       <c r="I23" s="22" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J23" s="22" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="K23" s="22" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="L23" s="23"/>
     </row>
@@ -2126,19 +2108,19 @@
         <v>5</v>
       </c>
       <c r="G24" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="H24" s="30" t="s">
-        <v>78</v>
+        <v>63</v>
+      </c>
+      <c r="H24" s="53" t="s">
+        <v>74</v>
       </c>
       <c r="I24" s="22" t="s">
-        <v>44</v>
+        <v>109</v>
       </c>
       <c r="J24" s="22" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="K24" s="22" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="L24" s="23"/>
     </row>
@@ -2160,19 +2142,19 @@
         <v>5</v>
       </c>
       <c r="G25" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="H25" s="30" t="s">
-        <v>79</v>
+        <v>64</v>
+      </c>
+      <c r="H25" s="53" t="s">
+        <v>75</v>
       </c>
       <c r="I25" s="21" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="J25" s="22" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="K25" s="22" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="L25" s="23"/>
     </row>
@@ -2194,22 +2176,22 @@
         <v>5</v>
       </c>
       <c r="G26" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="H26" s="31" t="s">
+        <v>65</v>
+      </c>
+      <c r="H26" s="51" t="s">
+        <v>78</v>
+      </c>
+      <c r="I26" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="J26" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="K26" s="22" t="s">
         <v>82</v>
       </c>
-      <c r="I26" s="21" t="s">
-        <v>45</v>
-      </c>
-      <c r="J26" s="22" t="s">
-        <v>109</v>
-      </c>
-      <c r="K26" s="22" t="s">
-        <v>86</v>
-      </c>
-      <c r="L26" s="29" t="s">
-        <v>76</v>
+      <c r="L26" s="52" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="27" spans="1:12" ht="56.45" customHeight="1">
@@ -2230,19 +2212,19 @@
         <v>5</v>
       </c>
       <c r="G27" s="16" t="s">
-        <v>70</v>
-      </c>
-      <c r="H27" s="30" t="s">
-        <v>80</v>
+        <v>66</v>
+      </c>
+      <c r="H27" s="53" t="s">
+        <v>76</v>
       </c>
       <c r="I27" s="21" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="J27" s="19" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="K27" s="22" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="L27" s="25"/>
     </row>
@@ -2264,17 +2246,17 @@
         <v>5</v>
       </c>
       <c r="G28" s="16" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="H28" s="26"/>
       <c r="I28" s="21" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="J28" s="19" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="K28" s="22" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="L28" s="24"/>
     </row>
@@ -2291,27 +2273,27 @@
       <c r="E29" s="18">
         <v>45979</v>
       </c>
-      <c r="F29" s="32">
+      <c r="F29" s="54">
         <f>DAYS360(C29,E29)+1</f>
         <v>2</v>
       </c>
       <c r="G29" s="16" t="s">
-        <v>72</v>
-      </c>
-      <c r="H29" s="30" t="s">
-        <v>81</v>
+        <v>68</v>
+      </c>
+      <c r="H29" s="53" t="s">
+        <v>77</v>
       </c>
       <c r="I29" s="21" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="J29" s="19" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="K29" s="22" t="s">
-        <v>86</v>
-      </c>
-      <c r="L29" s="27" t="s">
-        <v>73</v>
+        <v>82</v>
+      </c>
+      <c r="L29" s="52" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="30" spans="1:12" ht="47.25" customHeight="1" thickBot="1">
@@ -2338,7 +2320,7 @@
     </row>
     <row r="32" spans="1:12" s="5" customFormat="1" ht="26.25">
       <c r="B32" s="60" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C32" s="60"/>
       <c r="D32" s="60"/>
